--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7190" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7190" uniqueCount="739">
   <si>
     <t>Property</t>
   </si>
@@ -633,7 +633,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -920,6 +920,14 @@
     <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="LP89803-8"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Observation.category:second.id</t>
   </si>
   <si>
@@ -936,9 +944,6 @@
   </si>
   <si>
     <t>Observation.category:second.coding.system</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
   </si>
   <si>
     <t>Observation.category:second.coding.version</t>
@@ -1072,6 +1077,9 @@
   </si>
   <si>
     <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
   </si>
   <si>
     <t>Observation.code.coding.version</t>
@@ -5198,7 +5206,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
@@ -5963,7 +5971,7 @@
         <v>83</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>83</v>
@@ -6037,7 +6045,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>207</v>
@@ -6155,7 +6163,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>214</v>
@@ -6275,7 +6283,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>220</v>
@@ -6397,7 +6405,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>230</v>
@@ -6515,7 +6523,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>232</v>
@@ -6635,7 +6643,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>234</v>
@@ -6646,7 +6654,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>94</v>
@@ -6680,7 +6688,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>297</v>
+        <v>83</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -8092,7 +8100,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>94</v>
@@ -9572,7 +9580,7 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>297</v>
+        <v>342</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9649,10 +9657,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9769,10 +9777,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9812,7 +9820,7 @@
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9889,10 +9897,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9935,7 +9943,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -10009,10 +10017,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10131,10 +10139,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10253,10 +10261,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10279,19 +10287,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10340,7 +10348,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10355,19 +10363,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -10375,10 +10383,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10401,16 +10409,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10460,7 +10468,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10484,10 +10492,10 @@
         <v>331</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10495,14 +10503,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10521,19 +10529,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10582,7 +10590,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10597,19 +10605,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10617,14 +10625,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10643,19 +10651,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10704,7 +10712,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10719,19 +10727,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10739,10 +10747,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10765,16 +10773,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10824,7 +10832,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10845,13 +10853,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10859,10 +10867,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10885,19 +10893,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10946,7 +10954,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10961,19 +10969,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10981,10 +10989,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11010,16 +11018,16 @@
         <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -11048,7 +11056,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -11066,7 +11074,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -11075,7 +11083,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -11084,27 +11092,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11130,16 +11138,16 @@
         <v>191</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -11164,13 +11172,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -11188,7 +11196,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11197,7 +11205,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -11212,7 +11220,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -11223,14 +11231,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11252,16 +11260,16 @@
         <v>191</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -11286,13 +11294,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -11310,7 +11318,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11328,27 +11336,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11371,19 +11379,19 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11432,7 +11440,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11453,10 +11461,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11467,10 +11475,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11496,13 +11504,13 @@
         <v>191</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11531,10 +11539,10 @@
         <v>326</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11552,7 +11560,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11570,27 +11578,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11705,10 +11713,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11716,7 +11724,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>82</v>
@@ -11734,10 +11742,10 @@
         <v>140</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11823,13 +11831,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>83</v>
@@ -11851,16 +11859,16 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11945,10 +11953,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12063,10 +12071,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12092,10 +12100,10 @@
         <v>140</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12181,10 +12189,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12210,13 +12218,13 @@
         <v>108</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12224,7 +12232,7 @@
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>83</v>
@@ -12266,7 +12274,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>94</v>
@@ -12301,10 +12309,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12330,10 +12338,10 @@
         <v>191</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12364,7 +12372,7 @@
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12382,7 +12390,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12417,10 +12425,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12535,10 +12543,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12655,10 +12663,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12777,10 +12785,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12895,10 +12903,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13015,10 +13023,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13060,7 +13068,7 @@
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>83</v>
@@ -13137,10 +13145,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13257,10 +13265,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13377,10 +13385,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13497,10 +13505,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13619,10 +13627,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13741,13 +13749,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>83</v>
@@ -13769,13 +13777,13 @@
         <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13861,10 +13869,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13979,10 +13987,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14008,10 +14016,10 @@
         <v>140</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14097,13 +14105,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>83</v>
@@ -14128,10 +14136,10 @@
         <v>140</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14217,10 +14225,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14335,10 +14343,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14364,10 +14372,10 @@
         <v>140</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14453,10 +14461,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14482,13 +14490,13 @@
         <v>108</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14496,7 +14504,7 @@
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>83</v>
@@ -14538,7 +14546,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>94</v>
@@ -14573,10 +14581,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14602,10 +14610,10 @@
         <v>191</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14636,7 +14644,7 @@
       </c>
       <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>83</v>
@@ -14654,7 +14662,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14689,13 +14697,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>83</v>
@@ -14720,10 +14728,10 @@
         <v>140</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14809,10 +14817,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14927,10 +14935,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14956,10 +14964,10 @@
         <v>140</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15045,10 +15053,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15074,13 +15082,13 @@
         <v>108</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15088,7 +15096,7 @@
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>83</v>
@@ -15130,7 +15138,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>94</v>
@@ -15165,10 +15173,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15194,10 +15202,10 @@
         <v>191</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15248,7 +15256,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15283,13 +15291,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>83</v>
@@ -15314,10 +15322,10 @@
         <v>140</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15403,10 +15411,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15521,10 +15529,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15641,13 +15649,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>83</v>
@@ -15672,10 +15680,10 @@
         <v>140</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15761,10 +15769,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15879,10 +15887,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15908,10 +15916,10 @@
         <v>140</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15997,10 +16005,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16026,13 +16034,13 @@
         <v>108</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16040,7 +16048,7 @@
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="S112" t="s" s="2">
         <v>83</v>
@@ -16082,7 +16090,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>94</v>
@@ -16117,10 +16125,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16146,10 +16154,10 @@
         <v>191</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16200,7 +16208,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16235,13 +16243,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>83</v>
@@ -16266,10 +16274,10 @@
         <v>140</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16355,10 +16363,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16473,10 +16481,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16502,10 +16510,10 @@
         <v>140</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16591,10 +16599,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16620,13 +16628,13 @@
         <v>108</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -16634,7 +16642,7 @@
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>83</v>
@@ -16676,7 +16684,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>94</v>
@@ -16711,10 +16719,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16740,10 +16748,10 @@
         <v>191</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16794,7 +16802,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -16829,13 +16837,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>83</v>
@@ -16860,10 +16868,10 @@
         <v>140</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16949,10 +16957,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17067,10 +17075,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17187,13 +17195,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>83</v>
@@ -17218,10 +17226,10 @@
         <v>140</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17307,10 +17315,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17425,10 +17433,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17454,10 +17462,10 @@
         <v>140</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -17543,10 +17551,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17572,13 +17580,13 @@
         <v>108</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17586,7 +17594,7 @@
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="S125" t="s" s="2">
         <v>83</v>
@@ -17628,7 +17636,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>94</v>
@@ -17663,10 +17671,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17689,13 +17697,13 @@
         <v>83</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17746,7 +17754,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -17781,10 +17789,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17810,13 +17818,13 @@
         <v>108</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17824,7 +17832,7 @@
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>83</v>
@@ -17866,7 +17874,7 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>94</v>
@@ -17901,10 +17909,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17927,13 +17935,13 @@
         <v>83</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17984,7 +17992,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18019,13 +18027,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>83</v>
@@ -18050,10 +18058,10 @@
         <v>140</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -18139,10 +18147,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18257,10 +18265,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18286,10 +18294,10 @@
         <v>140</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -18375,10 +18383,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18404,13 +18412,13 @@
         <v>108</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18418,7 +18426,7 @@
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>83</v>
@@ -18460,7 +18468,7 @@
         <v>83</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>94</v>
@@ -18495,10 +18503,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18524,10 +18532,10 @@
         <v>191</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18578,7 +18586,7 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -18613,10 +18621,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18642,13 +18650,13 @@
         <v>108</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18656,7 +18664,7 @@
       </c>
       <c r="Q134" s="2"/>
       <c r="R134" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="S134" t="s" s="2">
         <v>83</v>
@@ -18698,7 +18706,7 @@
         <v>83</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>94</v>
@@ -18733,10 +18741,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18759,13 +18767,13 @@
         <v>83</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18816,7 +18824,7 @@
         <v>83</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -18851,13 +18859,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D136" t="s" s="2">
         <v>83</v>
@@ -18882,10 +18890,10 @@
         <v>140</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18971,10 +18979,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19089,10 +19097,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19118,10 +19126,10 @@
         <v>140</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19207,10 +19215,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19236,13 +19244,13 @@
         <v>108</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -19250,7 +19258,7 @@
       </c>
       <c r="Q139" s="2"/>
       <c r="R139" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="S139" t="s" s="2">
         <v>83</v>
@@ -19292,7 +19300,7 @@
         <v>83</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>94</v>
@@ -19327,10 +19335,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19356,10 +19364,10 @@
         <v>191</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19410,7 +19418,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -19445,10 +19453,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19563,10 +19571,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19683,10 +19691,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19758,7 +19766,7 @@
         <v>83</v>
       </c>
       <c r="AB143" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AC143" s="2"/>
       <c r="AD143" t="s" s="2">
@@ -19803,13 +19811,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D144" t="s" s="2">
         <v>83</v>
@@ -19834,10 +19842,10 @@
         <v>221</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>224</v>
@@ -19872,7 +19880,7 @@
       </c>
       <c r="Y144" s="2"/>
       <c r="Z144" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>83</v>
@@ -19925,10 +19933,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20043,10 +20051,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20163,10 +20171,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20208,7 +20216,7 @@
       </c>
       <c r="Q147" s="2"/>
       <c r="R147" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="S147" t="s" s="2">
         <v>83</v>
@@ -20285,10 +20293,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20405,10 +20413,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20525,10 +20533,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20645,10 +20653,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20767,13 +20775,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>83</v>
@@ -20798,10 +20806,10 @@
         <v>221</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N152" t="s" s="2">
         <v>224</v>
@@ -20836,7 +20844,7 @@
       </c>
       <c r="Y152" s="2"/>
       <c r="Z152" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>83</v>
@@ -20889,10 +20897,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21007,10 +21015,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21127,10 +21135,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21172,7 +21180,7 @@
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>83</v>
@@ -21249,10 +21257,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21369,10 +21377,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21489,10 +21497,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21609,10 +21617,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21731,10 +21739,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21853,10 +21861,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21882,13 +21890,13 @@
         <v>108</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -21896,7 +21904,7 @@
       </c>
       <c r="Q161" s="2"/>
       <c r="R161" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="S161" t="s" s="2">
         <v>83</v>
@@ -21938,7 +21946,7 @@
         <v>83</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>94</v>
@@ -21973,10 +21981,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21999,13 +22007,13 @@
         <v>83</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -22056,7 +22064,7 @@
         <v>83</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -22091,10 +22099,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22213,10 +22221,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22335,10 +22343,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22364,16 +22372,16 @@
         <v>191</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>83</v>
@@ -22401,10 +22409,10 @@
         <v>326</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>83</v>
@@ -22422,7 +22430,7 @@
         <v>83</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -22443,10 +22451,10 @@
         <v>83</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>83</v>
@@ -22457,10 +22465,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22483,16 +22491,16 @@
         <v>83</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -22542,7 +22550,7 @@
         <v>83</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -22560,27 +22568,27 @@
         <v>83</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22603,16 +22611,16 @@
         <v>83</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -22662,7 +22670,7 @@
         <v>83</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -22680,27 +22688,27 @@
         <v>83</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP167" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22723,19 +22731,19 @@
         <v>83</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>83</v>
@@ -22784,7 +22792,7 @@
         <v>83</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -22796,7 +22804,7 @@
         <v>83</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>83</v>
@@ -22805,10 +22813,10 @@
         <v>83</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>83</v>
@@ -22819,10 +22827,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22937,10 +22945,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23057,14 +23065,14 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
@@ -23086,10 +23094,10 @@
         <v>140</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N171" t="s" s="2">
         <v>143</v>
@@ -23144,7 +23152,7 @@
         <v>83</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>81</v>
@@ -23179,10 +23187,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23205,13 +23213,13 @@
         <v>83</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -23262,7 +23270,7 @@
         <v>83</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>81</v>
@@ -23271,7 +23279,7 @@
         <v>94</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>106</v>
@@ -23283,10 +23291,10 @@
         <v>83</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AO172" t="s" s="2">
         <v>83</v>
@@ -23297,10 +23305,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23323,13 +23331,13 @@
         <v>83</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -23380,7 +23388,7 @@
         <v>83</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
@@ -23389,7 +23397,7 @@
         <v>94</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AJ173" t="s" s="2">
         <v>106</v>
@@ -23401,10 +23409,10 @@
         <v>83</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>83</v>
@@ -23415,10 +23423,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23444,16 +23452,16 @@
         <v>191</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>83</v>
@@ -23481,10 +23489,10 @@
         <v>118</v>
       </c>
       <c r="Y174" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="Z174" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>83</v>
@@ -23502,7 +23510,7 @@
         <v>83</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
@@ -23520,13 +23528,13 @@
         <v>83</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>83</v>
@@ -23537,10 +23545,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23566,16 +23574,16 @@
         <v>191</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>83</v>
@@ -23603,10 +23611,10 @@
         <v>326</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>83</v>
@@ -23624,7 +23632,7 @@
         <v>83</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -23642,13 +23650,13 @@
         <v>83</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>83</v>
@@ -23659,10 +23667,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23685,17 +23693,17 @@
         <v>83</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>83</v>
@@ -23744,7 +23752,7 @@
         <v>83</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
@@ -23768,7 +23776,7 @@
         <v>83</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>83</v>
@@ -23779,10 +23787,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23808,10 +23816,10 @@
         <v>208</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
@@ -23862,7 +23870,7 @@
         <v>83</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
@@ -23883,10 +23891,10 @@
         <v>83</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>83</v>
@@ -23897,10 +23905,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23923,16 +23931,16 @@
         <v>95</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -23982,7 +23990,7 @@
         <v>83</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
@@ -24003,10 +24011,10 @@
         <v>83</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>83</v>
@@ -24017,10 +24025,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24043,16 +24051,16 @@
         <v>95</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
@@ -24102,7 +24110,7 @@
         <v>83</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
@@ -24123,10 +24131,10 @@
         <v>83</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>83</v>
@@ -24137,10 +24145,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24163,19 +24171,19 @@
         <v>95</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>83</v>
@@ -24224,7 +24232,7 @@
         <v>83</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
@@ -24245,10 +24253,10 @@
         <v>83</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AO180" t="s" s="2">
         <v>83</v>
@@ -24259,10 +24267,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24377,10 +24385,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24497,14 +24505,14 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -24526,10 +24534,10 @@
         <v>140</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N183" t="s" s="2">
         <v>143</v>
@@ -24584,7 +24592,7 @@
         <v>83</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
@@ -24619,10 +24627,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24648,13 +24656,13 @@
         <v>191</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="O184" t="s" s="2">
         <v>325</v>
@@ -24706,7 +24714,7 @@
         <v>83</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>94</v>
@@ -24724,7 +24732,7 @@
         <v>83</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AM184" t="s" s="2">
         <v>331</v>
@@ -24741,10 +24749,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24767,19 +24775,19 @@
         <v>95</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>83</v>
@@ -24828,7 +24836,7 @@
         <v>83</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>81</v>
@@ -24846,27 +24854,27 @@
         <v>83</v>
       </c>
       <c r="AL185" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP185" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24892,16 +24900,16 @@
         <v>191</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>83</v>
@@ -24926,13 +24934,13 @@
         <v>83</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Y186" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>83</v>
@@ -24950,7 +24958,7 @@
         <v>83</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>81</v>
@@ -24959,7 +24967,7 @@
         <v>94</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>106</v>
@@ -24974,7 +24982,7 @@
         <v>137</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO186" t="s" s="2">
         <v>83</v>
@@ -24985,14 +24993,14 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
@@ -25014,16 +25022,16 @@
         <v>191</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>83</v>
@@ -25048,13 +25056,13 @@
         <v>83</v>
       </c>
       <c r="X187" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Y187" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Z187" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AA187" t="s" s="2">
         <v>83</v>
@@ -25072,7 +25080,7 @@
         <v>83</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>81</v>
@@ -25090,27 +25098,27 @@
         <v>83</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP187" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25136,16 +25144,16 @@
         <v>84</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>83</v>
@@ -25194,7 +25202,7 @@
         <v>83</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>81</v>
@@ -25215,10 +25223,10 @@
         <v>83</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7190" uniqueCount="739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7190" uniqueCount="737">
   <si>
     <t>Property</t>
   </si>
@@ -658,6 +658,14 @@
     <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS"/&gt;
+    &lt;code value="exam"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
@@ -812,9 +820,6 @@
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>exam</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -952,9 +957,6 @@
     <t>Observation.category:second.coding.code</t>
   </si>
   <si>
-    <t>LP89803-8</t>
-  </si>
-  <si>
     <t>Observation.category:second.coding.display</t>
   </si>
   <si>
@@ -973,6 +975,14 @@
     <t>このObservationに関する詳細分類、JP_ObservationDetailedDentalCategory_VSより選択する、必須項目</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationDentalCategory_CS"/&gt;
+    &lt;code value="DO-1-04"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDetailedDentalCategory_VS</t>
   </si>
   <si>
@@ -994,16 +1004,10 @@
     <t>Observation.category:third.coding.system</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationDentalCategory_CS</t>
-  </si>
-  <si>
     <t>Observation.category:third.coding.version</t>
   </si>
   <si>
     <t>Observation.category:third.coding.code</t>
-  </si>
-  <si>
-    <t>DO-1-04</t>
   </si>
   <si>
     <t>Observation.category:third.coding.display</t>
@@ -1113,7 +1117,7 @@
     <t>観察対象者 【JP Core仕様】患者情報</t>
   </si>
   <si>
-    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明なデバイスによって観察が行われるケースである。この場合、観察は何らかのコンテキスト/チャネルマッチング技術を介して患者にマッチングされる必要があり、患者にマッチングされれば、その時点で本要素を更新する必要がある。</t>
+    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明な機器によって観察が行われるケースである。この場合、観察は何らかのコンテキスト・チャネル照合技術を介して患者に照合される必要があり、患者に照合されれば、その時点で本要素を更新する必要がある。</t>
   </si>
   <si>
     <t>あなたが彼らが誰または何をしているのかわからない場合、観察には価値がありません。 / Observations have no value if you don't know who or what they're about.</t>
@@ -1158,7 +1162,7 @@
 </t>
   </si>
   <si>
-    <t>このobservationが行われるヘルスケアイベント</t>
+    <t>このobservationが行われる診療イベント</t>
   </si>
   <si>
     <t>例：診療、歯科検診</t>
@@ -4525,7 +4529,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -4544,7 +4548,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -4597,10 +4601,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4623,13 +4627,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4680,7 +4684,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4704,7 +4708,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4715,10 +4719,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4747,7 +4751,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4788,10 +4792,10 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
@@ -4800,7 +4804,7 @@
         <v>198</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4824,7 +4828,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4835,10 +4839,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4861,19 +4865,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4922,7 +4926,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4943,10 +4947,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4957,10 +4961,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4983,13 +4987,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -5040,7 +5044,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -5064,7 +5068,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -5075,10 +5079,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5107,7 +5111,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -5148,10 +5152,10 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
@@ -5160,7 +5164,7 @@
         <v>198</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -5184,7 +5188,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -5195,10 +5199,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5224,23 +5228,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -5282,7 +5286,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5303,10 +5307,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -5317,10 +5321,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5343,16 +5347,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5402,7 +5406,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5423,10 +5427,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -5437,10 +5441,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5466,21 +5470,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>256</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -5583,7 +5587,7 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>262</v>
@@ -5825,7 +5829,7 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>280</v>
@@ -6048,7 +6052,7 @@
         <v>292</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6071,13 +6075,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -6128,7 +6132,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -6152,7 +6156,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -6166,7 +6170,7 @@
         <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6195,7 +6199,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -6236,10 +6240,10 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
@@ -6248,7 +6252,7 @@
         <v>198</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -6272,7 +6276,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -6286,7 +6290,7 @@
         <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6309,19 +6313,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -6370,7 +6374,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6391,10 +6395,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -6408,7 +6412,7 @@
         <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6431,13 +6435,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6488,7 +6492,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6512,7 +6516,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6526,7 +6530,7 @@
         <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6555,7 +6559,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -6596,10 +6600,10 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
@@ -6608,7 +6612,7 @@
         <v>198</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6632,7 +6636,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6646,7 +6650,7 @@
         <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6672,16 +6676,16 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6730,7 +6734,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6751,10 +6755,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6768,7 +6772,7 @@
         <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6791,16 +6795,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6850,7 +6854,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6871,10 +6875,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6888,7 +6892,7 @@
         <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6914,21 +6918,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -7005,7 +7009,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>261</v>
@@ -7031,7 +7035,7 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>262</v>
@@ -7125,7 +7129,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>269</v>
@@ -7247,7 +7251,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>279</v>
@@ -7273,7 +7277,7 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>280</v>
@@ -7369,13 +7373,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>189</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -7400,10 +7404,10 @@
         <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>290</v>
@@ -7419,7 +7423,7 @@
         <v>83</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>83</v>
@@ -7494,7 +7498,7 @@
         <v>308</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7517,13 +7521,13 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7574,7 +7578,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7598,7 +7602,7 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7612,7 +7616,7 @@
         <v>309</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7641,7 +7645,7 @@
         <v>141</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>143</v>
@@ -7682,10 +7686,10 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>83</v>
@@ -7694,7 +7698,7 @@
         <v>198</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7718,7 +7722,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7732,7 +7736,7 @@
         <v>310</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7755,19 +7759,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7816,7 +7820,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7837,10 +7841,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7854,7 +7858,7 @@
         <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7877,13 +7881,13 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7934,7 +7938,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7958,7 +7962,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7972,7 +7976,7 @@
         <v>312</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8001,7 +8005,7 @@
         <v>141</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>143</v>
@@ -8042,10 +8046,10 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>83</v>
@@ -8054,7 +8058,7 @@
         <v>198</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -8078,7 +8082,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -8092,7 +8096,7 @@
         <v>313</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8118,23 +8122,23 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>314</v>
+        <v>83</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -8176,7 +8180,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -8197,10 +8201,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -8211,10 +8215,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8237,16 +8241,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8296,7 +8300,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8317,10 +8321,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -8331,10 +8335,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8360,21 +8364,21 @@
         <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>83</v>
@@ -8451,7 +8455,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>261</v>
@@ -8477,7 +8481,7 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>262</v>
@@ -8571,7 +8575,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>269</v>
@@ -8693,7 +8697,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>279</v>
@@ -8719,7 +8723,7 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>280</v>
@@ -8815,14 +8819,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8844,16 +8848,16 @@
         <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8878,14 +8882,14 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="Y52" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8902,7 +8906,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>94</v>
@@ -8917,30 +8921,30 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>334</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8963,13 +8967,13 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9020,7 +9024,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -9044,7 +9048,7 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -9055,10 +9059,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9087,7 +9091,7 @@
         <v>141</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>143</v>
@@ -9128,10 +9132,10 @@
         <v>83</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>83</v>
@@ -9140,7 +9144,7 @@
         <v>198</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -9164,7 +9168,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -9175,10 +9179,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9201,19 +9205,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -9262,7 +9266,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9283,10 +9287,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -9297,10 +9301,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9323,13 +9327,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9380,7 +9384,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9404,7 +9408,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -9415,10 +9419,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9447,7 +9451,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -9488,10 +9492,10 @@
         <v>83</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>83</v>
@@ -9500,7 +9504,7 @@
         <v>198</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9524,7 +9528,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -9535,10 +9539,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9564,23 +9568,23 @@
         <v>108</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9622,7 +9626,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9643,10 +9647,10 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9657,10 +9661,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9683,16 +9687,16 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9742,7 +9746,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9763,10 +9767,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9777,10 +9781,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9806,21 +9810,21 @@
         <v>114</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9897,10 +9901,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9923,7 +9927,7 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>262</v>
@@ -9943,7 +9947,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -10017,10 +10021,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10139,10 +10143,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10165,7 +10169,7 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>280</v>
@@ -10261,10 +10265,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10287,19 +10291,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10348,7 +10352,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10363,19 +10367,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AL64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -10383,10 +10387,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10409,16 +10413,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10468,7 +10472,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10489,13 +10493,13 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10503,14 +10507,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10529,19 +10533,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10590,7 +10594,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10605,19 +10609,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AL66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10625,14 +10629,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10651,19 +10655,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10712,7 +10716,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10727,19 +10731,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AL67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10747,10 +10751,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10773,16 +10777,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10832,7 +10836,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10853,13 +10857,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10867,10 +10871,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10893,19 +10897,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10954,7 +10958,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10969,19 +10973,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AL69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10989,10 +10993,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11018,16 +11022,16 @@
         <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="O70" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -11056,7 +11060,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -11074,7 +11078,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -11083,7 +11087,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -11092,27 +11096,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>409</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11138,16 +11142,16 @@
         <v>191</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="O71" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -11172,40 +11176,40 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="Y71" t="s" s="2">
+      <c r="AA71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI71" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -11220,7 +11224,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -11231,14 +11235,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11260,16 +11264,16 @@
         <v>191</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="O72" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -11294,13 +11298,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -11318,7 +11322,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11336,27 +11340,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>429</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11379,19 +11383,19 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11440,7 +11444,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11461,10 +11465,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11475,10 +11479,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11504,13 +11508,13 @@
         <v>191</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11536,13 +11540,13 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11560,7 +11564,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11578,27 +11582,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11621,13 +11625,13 @@
         <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11678,7 +11682,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11702,7 +11706,7 @@
         <v>83</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11713,10 +11717,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11724,7 +11728,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>82</v>
@@ -11742,10 +11746,10 @@
         <v>140</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11784,10 +11788,10 @@
         <v>83</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>83</v>
@@ -11796,7 +11800,7 @@
         <v>198</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11831,13 +11835,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>83</v>
@@ -11859,16 +11863,16 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11918,7 +11922,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11953,10 +11957,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11979,13 +11983,13 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12036,7 +12040,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -12060,7 +12064,7 @@
         <v>83</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -12071,10 +12075,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12100,10 +12104,10 @@
         <v>140</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12142,10 +12146,10 @@
         <v>83</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>83</v>
@@ -12154,7 +12158,7 @@
         <v>198</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12189,10 +12193,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12218,13 +12222,13 @@
         <v>108</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12232,7 +12236,7 @@
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>83</v>
@@ -12274,7 +12278,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>94</v>
@@ -12309,10 +12313,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12338,10 +12342,10 @@
         <v>191</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12372,7 +12376,7 @@
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12390,7 +12394,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12425,10 +12429,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12451,13 +12455,13 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12508,7 +12512,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12532,7 +12536,7 @@
         <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12543,10 +12547,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12575,7 +12579,7 @@
         <v>141</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>143</v>
@@ -12616,10 +12620,10 @@
         <v>83</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>83</v>
@@ -12628,7 +12632,7 @@
         <v>198</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12652,7 +12656,7 @@
         <v>83</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12663,10 +12667,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12689,19 +12693,19 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12750,7 +12754,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12771,10 +12775,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12785,10 +12789,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12811,13 +12815,13 @@
         <v>83</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12868,7 +12872,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12892,7 +12896,7 @@
         <v>83</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12903,10 +12907,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12935,7 +12939,7 @@
         <v>141</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>143</v>
@@ -12976,10 +12980,10 @@
         <v>83</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>83</v>
@@ -12988,7 +12992,7 @@
         <v>198</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -13012,7 +13016,7 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -13023,10 +13027,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13052,23 +13056,23 @@
         <v>108</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>83</v>
@@ -13110,7 +13114,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -13131,10 +13135,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -13145,10 +13149,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13171,16 +13175,16 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13230,7 +13234,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13251,10 +13255,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -13265,10 +13269,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13294,14 +13298,14 @@
         <v>114</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -13385,10 +13389,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13411,7 +13415,7 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>262</v>
@@ -13505,10 +13509,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13627,10 +13631,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13653,7 +13657,7 @@
         <v>95</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L92" t="s" s="2">
         <v>280</v>
@@ -13749,13 +13753,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>83</v>
@@ -13777,13 +13781,13 @@
         <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13834,7 +13838,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13869,10 +13873,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13895,13 +13899,13 @@
         <v>83</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13952,7 +13956,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13976,7 +13980,7 @@
         <v>83</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
@@ -13987,10 +13991,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14016,10 +14020,10 @@
         <v>140</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14058,10 +14062,10 @@
         <v>83</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>83</v>
@@ -14070,7 +14074,7 @@
         <v>198</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14105,13 +14109,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>83</v>
@@ -14136,10 +14140,10 @@
         <v>140</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14190,7 +14194,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14225,10 +14229,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14251,13 +14255,13 @@
         <v>83</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14308,7 +14312,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14332,7 +14336,7 @@
         <v>83</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
@@ -14343,10 +14347,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14372,10 +14376,10 @@
         <v>140</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14414,10 +14418,10 @@
         <v>83</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>83</v>
@@ -14426,7 +14430,7 @@
         <v>198</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14461,10 +14465,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14490,13 +14494,13 @@
         <v>108</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N99" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14504,7 +14508,7 @@
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>83</v>
@@ -14546,7 +14550,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>94</v>
@@ -14581,10 +14585,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14610,10 +14614,10 @@
         <v>191</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14644,7 +14648,7 @@
       </c>
       <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>83</v>
@@ -14662,7 +14666,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14697,13 +14701,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>83</v>
@@ -14728,10 +14732,10 @@
         <v>140</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14782,7 +14786,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14817,10 +14821,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14843,13 +14847,13 @@
         <v>83</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14900,7 +14904,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14924,7 +14928,7 @@
         <v>83</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14935,10 +14939,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14964,10 +14968,10 @@
         <v>140</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15006,10 +15010,10 @@
         <v>83</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>83</v>
@@ -15018,7 +15022,7 @@
         <v>198</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -15053,10 +15057,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15082,13 +15086,13 @@
         <v>108</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N104" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15096,7 +15100,7 @@
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>83</v>
@@ -15138,7 +15142,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>94</v>
@@ -15173,10 +15177,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15202,10 +15206,10 @@
         <v>191</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15256,7 +15260,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15291,13 +15295,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>83</v>
@@ -15322,10 +15326,10 @@
         <v>140</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15376,7 +15380,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15411,10 +15415,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15437,13 +15441,13 @@
         <v>83</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15494,7 +15498,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15518,7 +15522,7 @@
         <v>83</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15529,10 +15533,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15561,7 +15565,7 @@
         <v>141</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>143</v>
@@ -15602,10 +15606,10 @@
         <v>83</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>83</v>
@@ -15614,7 +15618,7 @@
         <v>198</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15638,7 +15642,7 @@
         <v>83</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>83</v>
@@ -15649,13 +15653,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>83</v>
@@ -15680,10 +15684,10 @@
         <v>140</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15734,7 +15738,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15769,10 +15773,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15795,13 +15799,13 @@
         <v>83</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15852,7 +15856,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15876,7 +15880,7 @@
         <v>83</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>83</v>
@@ -15887,10 +15891,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15916,10 +15920,10 @@
         <v>140</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15958,10 +15962,10 @@
         <v>83</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>83</v>
@@ -15970,7 +15974,7 @@
         <v>198</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16005,10 +16009,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16034,13 +16038,13 @@
         <v>108</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N112" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16048,7 +16052,7 @@
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="S112" t="s" s="2">
         <v>83</v>
@@ -16090,7 +16094,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>94</v>
@@ -16125,10 +16129,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16154,10 +16158,10 @@
         <v>191</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16208,7 +16212,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16243,13 +16247,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>83</v>
@@ -16274,10 +16278,10 @@
         <v>140</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16328,7 +16332,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16363,10 +16367,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16389,13 +16393,13 @@
         <v>83</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16446,7 +16450,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16470,7 +16474,7 @@
         <v>83</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
@@ -16481,10 +16485,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16510,10 +16514,10 @@
         <v>140</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16552,10 +16556,10 @@
         <v>83</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC116" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD116" t="s" s="2">
         <v>83</v>
@@ -16564,7 +16568,7 @@
         <v>198</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -16599,10 +16603,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16628,13 +16632,13 @@
         <v>108</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N117" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -16642,7 +16646,7 @@
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>83</v>
@@ -16684,7 +16688,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>94</v>
@@ -16719,10 +16723,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16748,10 +16752,10 @@
         <v>191</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16802,7 +16806,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -16837,13 +16841,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>83</v>
@@ -16868,10 +16872,10 @@
         <v>140</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16922,7 +16926,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -16957,10 +16961,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16983,13 +16987,13 @@
         <v>83</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -17040,7 +17044,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17064,7 +17068,7 @@
         <v>83</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>83</v>
@@ -17075,10 +17079,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17107,7 +17111,7 @@
         <v>141</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>143</v>
@@ -17148,10 +17152,10 @@
         <v>83</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>83</v>
@@ -17160,7 +17164,7 @@
         <v>198</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -17184,7 +17188,7 @@
         <v>83</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>83</v>
@@ -17195,13 +17199,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>83</v>
@@ -17226,10 +17230,10 @@
         <v>140</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17280,7 +17284,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17315,10 +17319,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17341,13 +17345,13 @@
         <v>83</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -17398,7 +17402,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17422,7 +17426,7 @@
         <v>83</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>83</v>
@@ -17433,10 +17437,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17462,10 +17466,10 @@
         <v>140</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -17504,10 +17508,10 @@
         <v>83</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC124" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD124" t="s" s="2">
         <v>83</v>
@@ -17516,7 +17520,7 @@
         <v>198</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -17551,10 +17555,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17580,13 +17584,13 @@
         <v>108</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N125" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17594,7 +17598,7 @@
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="S125" t="s" s="2">
         <v>83</v>
@@ -17636,7 +17640,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>94</v>
@@ -17671,10 +17675,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17697,13 +17701,13 @@
         <v>83</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17754,7 +17758,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -17789,10 +17793,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17818,13 +17822,13 @@
         <v>108</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N127" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17832,7 +17836,7 @@
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>83</v>
@@ -17874,7 +17878,7 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>94</v>
@@ -17909,10 +17913,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17935,13 +17939,13 @@
         <v>83</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17992,7 +17996,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18027,13 +18031,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>83</v>
@@ -18058,10 +18062,10 @@
         <v>140</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -18112,7 +18116,7 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -18147,10 +18151,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18173,13 +18177,13 @@
         <v>83</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18230,7 +18234,7 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -18254,7 +18258,7 @@
         <v>83</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>83</v>
@@ -18265,10 +18269,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18294,10 +18298,10 @@
         <v>140</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -18336,10 +18340,10 @@
         <v>83</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>83</v>
@@ -18348,7 +18352,7 @@
         <v>198</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -18383,10 +18387,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18412,13 +18416,13 @@
         <v>108</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N132" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18426,7 +18430,7 @@
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>83</v>
@@ -18468,7 +18472,7 @@
         <v>83</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>94</v>
@@ -18503,10 +18507,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18532,10 +18536,10 @@
         <v>191</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18586,7 +18590,7 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -18621,10 +18625,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18650,13 +18654,13 @@
         <v>108</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N134" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18664,7 +18668,7 @@
       </c>
       <c r="Q134" s="2"/>
       <c r="R134" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="S134" t="s" s="2">
         <v>83</v>
@@ -18706,7 +18710,7 @@
         <v>83</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>94</v>
@@ -18741,10 +18745,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18767,13 +18771,13 @@
         <v>83</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18824,7 +18828,7 @@
         <v>83</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -18859,13 +18863,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D136" t="s" s="2">
         <v>83</v>
@@ -18890,10 +18894,10 @@
         <v>140</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18944,7 +18948,7 @@
         <v>83</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -18979,10 +18983,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19005,13 +19009,13 @@
         <v>83</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -19062,7 +19066,7 @@
         <v>83</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -19086,7 +19090,7 @@
         <v>83</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>83</v>
@@ -19097,10 +19101,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19126,10 +19130,10 @@
         <v>140</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19168,10 +19172,10 @@
         <v>83</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>83</v>
@@ -19180,7 +19184,7 @@
         <v>198</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -19215,10 +19219,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19244,13 +19248,13 @@
         <v>108</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N139" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -19258,7 +19262,7 @@
       </c>
       <c r="Q139" s="2"/>
       <c r="R139" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="S139" t="s" s="2">
         <v>83</v>
@@ -19300,7 +19304,7 @@
         <v>83</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>94</v>
@@ -19335,10 +19339,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19364,10 +19368,10 @@
         <v>191</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19418,7 +19422,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -19453,10 +19457,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19479,13 +19483,13 @@
         <v>83</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19536,7 +19540,7 @@
         <v>83</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
@@ -19560,7 +19564,7 @@
         <v>83</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>83</v>
@@ -19571,10 +19575,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19603,7 +19607,7 @@
         <v>141</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N142" t="s" s="2">
         <v>143</v>
@@ -19644,10 +19648,10 @@
         <v>83</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>83</v>
@@ -19656,7 +19660,7 @@
         <v>198</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
@@ -19680,7 +19684,7 @@
         <v>83</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>83</v>
@@ -19691,10 +19695,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19717,19 +19721,19 @@
         <v>95</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>83</v>
@@ -19766,7 +19770,7 @@
         <v>83</v>
       </c>
       <c r="AB143" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="AC143" s="2"/>
       <c r="AD143" t="s" s="2">
@@ -19776,7 +19780,7 @@
         <v>198</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
@@ -19797,10 +19801,10 @@
         <v>83</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>83</v>
@@ -19811,13 +19815,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D144" t="s" s="2">
         <v>83</v>
@@ -19839,19 +19843,19 @@
         <v>95</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>83</v>
@@ -19880,7 +19884,7 @@
       </c>
       <c r="Y144" s="2"/>
       <c r="Z144" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>83</v>
@@ -19898,7 +19902,7 @@
         <v>83</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>81</v>
@@ -19919,10 +19923,10 @@
         <v>83</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>83</v>
@@ -19933,10 +19937,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19959,13 +19963,13 @@
         <v>83</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -20016,7 +20020,7 @@
         <v>83</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -20040,7 +20044,7 @@
         <v>83</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>83</v>
@@ -20051,10 +20055,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20083,7 +20087,7 @@
         <v>141</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N146" t="s" s="2">
         <v>143</v>
@@ -20124,10 +20128,10 @@
         <v>83</v>
       </c>
       <c r="AB146" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC146" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD146" t="s" s="2">
         <v>83</v>
@@ -20136,7 +20140,7 @@
         <v>198</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -20160,7 +20164,7 @@
         <v>83</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>83</v>
@@ -20171,10 +20175,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20200,23 +20204,23 @@
         <v>108</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q147" s="2"/>
       <c r="R147" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="S147" t="s" s="2">
         <v>83</v>
@@ -20258,7 +20262,7 @@
         <v>83</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
@@ -20279,10 +20283,10 @@
         <v>83</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>83</v>
@@ -20293,10 +20297,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20319,16 +20323,16 @@
         <v>95</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -20378,7 +20382,7 @@
         <v>83</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>81</v>
@@ -20399,10 +20403,10 @@
         <v>83</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>83</v>
@@ -20413,10 +20417,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20442,14 +20446,14 @@
         <v>114</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>83</v>
@@ -20533,10 +20537,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20559,7 +20563,7 @@
         <v>95</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L150" t="s" s="2">
         <v>262</v>
@@ -20653,10 +20657,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20775,13 +20779,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>83</v>
@@ -20803,19 +20807,19 @@
         <v>95</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>83</v>
@@ -20844,7 +20848,7 @@
       </c>
       <c r="Y152" s="2"/>
       <c r="Z152" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>83</v>
@@ -20862,7 +20866,7 @@
         <v>83</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -20883,10 +20887,10 @@
         <v>83</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>83</v>
@@ -20897,10 +20901,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20923,13 +20927,13 @@
         <v>83</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -20980,7 +20984,7 @@
         <v>83</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>81</v>
@@ -21004,7 +21008,7 @@
         <v>83</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>83</v>
@@ -21015,10 +21019,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21047,7 +21051,7 @@
         <v>141</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N154" t="s" s="2">
         <v>143</v>
@@ -21088,10 +21092,10 @@
         <v>83</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>83</v>
@@ -21100,7 +21104,7 @@
         <v>198</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -21124,7 +21128,7 @@
         <v>83</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>83</v>
@@ -21135,10 +21139,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21164,23 +21168,23 @@
         <v>108</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>83</v>
@@ -21222,7 +21226,7 @@
         <v>83</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -21243,10 +21247,10 @@
         <v>83</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>83</v>
@@ -21257,10 +21261,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21283,16 +21287,16 @@
         <v>95</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -21342,7 +21346,7 @@
         <v>83</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -21363,10 +21367,10 @@
         <v>83</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>83</v>
@@ -21377,10 +21381,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21406,14 +21410,14 @@
         <v>114</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>83</v>
@@ -21497,10 +21501,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21523,7 +21527,7 @@
         <v>95</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L158" t="s" s="2">
         <v>262</v>
@@ -21617,10 +21621,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21739,10 +21743,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21765,7 +21769,7 @@
         <v>95</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L160" t="s" s="2">
         <v>280</v>
@@ -21861,10 +21865,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21890,13 +21894,13 @@
         <v>108</v>
       </c>
       <c r="L161" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M161" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N161" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -21904,7 +21908,7 @@
       </c>
       <c r="Q161" s="2"/>
       <c r="R161" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="S161" t="s" s="2">
         <v>83</v>
@@ -21946,7 +21950,7 @@
         <v>83</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>94</v>
@@ -21981,10 +21985,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22007,13 +22011,13 @@
         <v>83</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -22064,7 +22068,7 @@
         <v>83</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -22099,10 +22103,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22125,19 +22129,19 @@
         <v>95</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>83</v>
@@ -22186,7 +22190,7 @@
         <v>83</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -22207,10 +22211,10 @@
         <v>83</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>83</v>
@@ -22221,10 +22225,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22247,7 +22251,7 @@
         <v>95</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L164" t="s" s="2">
         <v>280</v>
@@ -22343,10 +22347,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22372,16 +22376,16 @@
         <v>191</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M165" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="N165" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="O165" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>83</v>
@@ -22406,13 +22410,13 @@
         <v>83</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>83</v>
@@ -22430,7 +22434,7 @@
         <v>83</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -22451,10 +22455,10 @@
         <v>83</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>83</v>
@@ -22465,10 +22469,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22491,16 +22495,16 @@
         <v>83</v>
       </c>
       <c r="K166" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="L166" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M166" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="N166" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="L166" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -22550,7 +22554,7 @@
         <v>83</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -22568,27 +22572,27 @@
         <v>83</v>
       </c>
       <c r="AL166" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AM166" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AN166" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="AM166" t="s" s="2">
+      <c r="AO166" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP166" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="AN166" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="AO166" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP166" t="s" s="2">
-        <v>633</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22611,16 +22615,16 @@
         <v>83</v>
       </c>
       <c r="K167" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="L167" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M167" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="N167" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="L167" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="M167" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -22670,7 +22674,7 @@
         <v>83</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -22688,27 +22692,27 @@
         <v>83</v>
       </c>
       <c r="AL167" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AM167" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AN167" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="AM167" t="s" s="2">
+      <c r="AO167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP167" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="AN167" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="AO167" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP167" t="s" s="2">
-        <v>641</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22731,19 +22735,19 @@
         <v>83</v>
       </c>
       <c r="K168" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="L168" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M168" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="N168" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="L168" t="s" s="2">
+      <c r="O168" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>83</v>
@@ -22792,7 +22796,7 @@
         <v>83</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -22804,19 +22808,19 @@
         <v>83</v>
       </c>
       <c r="AJ168" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AK168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM168" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AN168" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="AK168" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL168" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM168" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="AN168" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>83</v>
@@ -22827,10 +22831,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22853,13 +22857,13 @@
         <v>83</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -22910,7 +22914,7 @@
         <v>83</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
@@ -22934,7 +22938,7 @@
         <v>83</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>83</v>
@@ -22945,10 +22949,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22977,7 +22981,7 @@
         <v>141</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N170" t="s" s="2">
         <v>143</v>
@@ -23030,7 +23034,7 @@
         <v>83</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
@@ -23054,7 +23058,7 @@
         <v>83</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>83</v>
@@ -23065,14 +23069,14 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
@@ -23094,10 +23098,10 @@
         <v>140</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="N171" t="s" s="2">
         <v>143</v>
@@ -23152,7 +23156,7 @@
         <v>83</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>81</v>
@@ -23187,10 +23191,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23213,13 +23217,13 @@
         <v>83</v>
       </c>
       <c r="K172" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="L172" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="L172" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -23270,7 +23274,7 @@
         <v>83</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>81</v>
@@ -23279,7 +23283,7 @@
         <v>94</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>106</v>
@@ -23291,10 +23295,10 @@
         <v>83</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="AO172" t="s" s="2">
         <v>83</v>
@@ -23305,10 +23309,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23331,13 +23335,13 @@
         <v>83</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -23388,7 +23392,7 @@
         <v>83</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
@@ -23397,7 +23401,7 @@
         <v>94</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="AJ173" t="s" s="2">
         <v>106</v>
@@ -23409,10 +23413,10 @@
         <v>83</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>83</v>
@@ -23423,10 +23427,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23452,16 +23456,16 @@
         <v>191</v>
       </c>
       <c r="L174" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="M174" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="N174" t="s" s="2">
         <v>669</v>
       </c>
-      <c r="M174" t="s" s="2">
+      <c r="O174" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="O174" t="s" s="2">
-        <v>672</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>83</v>
@@ -23489,10 +23493,10 @@
         <v>118</v>
       </c>
       <c r="Y174" t="s" s="2">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="Z174" t="s" s="2">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>83</v>
@@ -23510,7 +23514,7 @@
         <v>83</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
@@ -23528,13 +23532,13 @@
         <v>83</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>83</v>
@@ -23545,10 +23549,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23574,16 +23578,16 @@
         <v>191</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="M175" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="N175" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="M175" t="s" s="2">
+      <c r="O175" t="s" s="2">
         <v>679</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="O175" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>83</v>
@@ -23608,13 +23612,13 @@
         <v>83</v>
       </c>
       <c r="X175" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>83</v>
@@ -23632,7 +23636,7 @@
         <v>83</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -23650,13 +23654,13 @@
         <v>83</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>83</v>
@@ -23667,10 +23671,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23693,17 +23697,17 @@
         <v>83</v>
       </c>
       <c r="K176" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="L176" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="M176" t="s" s="2">
         <v>685</v>
-      </c>
-      <c r="L176" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" t="s" s="2">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>83</v>
@@ -23752,7 +23756,7 @@
         <v>83</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
@@ -23776,7 +23780,7 @@
         <v>83</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>83</v>
@@ -23787,10 +23791,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23813,13 +23817,13 @@
         <v>83</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
@@ -23870,7 +23874,7 @@
         <v>83</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
@@ -23891,10 +23895,10 @@
         <v>83</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>83</v>
@@ -23905,10 +23909,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23931,16 +23935,16 @@
         <v>95</v>
       </c>
       <c r="K178" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="L178" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="M178" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="N178" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="L178" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="M178" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -23990,7 +23994,7 @@
         <v>83</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
@@ -24011,10 +24015,10 @@
         <v>83</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>83</v>
@@ -24025,10 +24029,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24051,16 +24055,16 @@
         <v>95</v>
       </c>
       <c r="K179" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="L179" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="M179" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="N179" t="s" s="2">
         <v>701</v>
-      </c>
-      <c r="L179" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
@@ -24110,7 +24114,7 @@
         <v>83</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
@@ -24131,10 +24135,10 @@
         <v>83</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>83</v>
@@ -24145,10 +24149,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24171,19 +24175,19 @@
         <v>95</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="L180" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="M180" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="N180" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="O180" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="M180" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="O180" t="s" s="2">
-        <v>708</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>83</v>
@@ -24232,7 +24236,7 @@
         <v>83</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
@@ -24253,10 +24257,10 @@
         <v>83</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="AO180" t="s" s="2">
         <v>83</v>
@@ -24267,10 +24271,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24293,13 +24297,13 @@
         <v>83</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
@@ -24350,7 +24354,7 @@
         <v>83</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>81</v>
@@ -24374,7 +24378,7 @@
         <v>83</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO181" t="s" s="2">
         <v>83</v>
@@ -24385,10 +24389,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24417,7 +24421,7 @@
         <v>141</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N182" t="s" s="2">
         <v>143</v>
@@ -24470,7 +24474,7 @@
         <v>83</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>81</v>
@@ -24494,7 +24498,7 @@
         <v>83</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>83</v>
@@ -24505,14 +24509,14 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -24534,10 +24538,10 @@
         <v>140</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="N183" t="s" s="2">
         <v>143</v>
@@ -24592,7 +24596,7 @@
         <v>83</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
@@ -24627,10 +24631,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24656,16 +24660,16 @@
         <v>191</v>
       </c>
       <c r="L184" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="M184" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="N184" t="s" s="2">
         <v>715</v>
       </c>
-      <c r="M184" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="N184" t="s" s="2">
-        <v>717</v>
-      </c>
       <c r="O184" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>83</v>
@@ -24690,14 +24694,14 @@
         <v>83</v>
       </c>
       <c r="X184" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Y184" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z184" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="Y184" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="Z184" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="AA184" t="s" s="2">
         <v>83</v>
       </c>
@@ -24714,7 +24718,7 @@
         <v>83</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>94</v>
@@ -24732,16 +24736,16 @@
         <v>83</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="AM184" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AN184" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AO184" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AN184" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AO184" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AP184" t="s" s="2">
         <v>83</v>
@@ -24749,10 +24753,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24775,19 +24779,19 @@
         <v>95</v>
       </c>
       <c r="K185" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="L185" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="M185" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="L185" t="s" s="2">
+      <c r="N185" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="M185" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>723</v>
-      </c>
       <c r="O185" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>83</v>
@@ -24836,7 +24840,7 @@
         <v>83</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>81</v>
@@ -24854,27 +24858,27 @@
         <v>83</v>
       </c>
       <c r="AL185" t="s" s="2">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="AM185" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AN185" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AO185" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP185" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AN185" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AO185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP185" t="s" s="2">
-        <v>409</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24900,16 +24904,16 @@
         <v>191</v>
       </c>
       <c r="L186" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="M186" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="N186" t="s" s="2">
         <v>726</v>
       </c>
-      <c r="M186" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="N186" t="s" s="2">
-        <v>728</v>
-      </c>
       <c r="O186" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>83</v>
@@ -24934,40 +24938,40 @@
         <v>83</v>
       </c>
       <c r="X186" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Y186" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="Z186" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="Y186" t="s" s="2">
+      <c r="AA186" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB186" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC186" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD186" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE186" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF186" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="AG186" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH186" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI186" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="Z186" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AA186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF186" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="AG186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH186" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI186" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>106</v>
@@ -24982,7 +24986,7 @@
         <v>137</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AO186" t="s" s="2">
         <v>83</v>
@@ -24993,14 +24997,14 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
@@ -25022,16 +25026,16 @@
         <v>191</v>
       </c>
       <c r="L187" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="M187" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="N187" t="s" s="2">
         <v>730</v>
       </c>
-      <c r="M187" t="s" s="2">
+      <c r="O187" t="s" s="2">
         <v>731</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>733</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>83</v>
@@ -25056,13 +25060,13 @@
         <v>83</v>
       </c>
       <c r="X187" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Y187" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="Z187" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AA187" t="s" s="2">
         <v>83</v>
@@ -25080,7 +25084,7 @@
         <v>83</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>81</v>
@@ -25098,27 +25102,27 @@
         <v>83</v>
       </c>
       <c r="AL187" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AM187" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN187" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AM187" t="s" s="2">
+      <c r="AO187" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP187" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AN187" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AO187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP187" t="s" s="2">
-        <v>429</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25144,16 +25148,16 @@
         <v>84</v>
       </c>
       <c r="L188" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="M188" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="N188" t="s" s="2">
         <v>735</v>
       </c>
-      <c r="M188" t="s" s="2">
+      <c r="O188" t="s" s="2">
         <v>736</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="O188" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>83</v>
@@ -25202,7 +25206,7 @@
         <v>83</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>81</v>
@@ -25223,10 +25227,10 @@
         <v>83</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>83</v>
